--- a/SampleLogging/1/student/CuongNHE186494/TC1/GradeDetail.xlsx
+++ b/SampleLogging/1/student/CuongNHE186494/TC1/GradeDetail.xlsx
@@ -5,10 +5,10 @@
   <x:workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\School\NET\auto-grading\HTTP_1\TC1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyTestCaseshoang\TCP_1\Q1\TC1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA2B170-0C20-4B09-8157-7418F082F6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE54D8B1-DCC7-4AAA-A5AB-081A77706533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
     <x:workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="0" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </x:bookViews>
@@ -45,199 +45,162 @@
     <x:t>StartServer</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve"> 1</x:t>
+    <x:t>1 + 2</x:t>
   </x:si>
   <x:si>
     <x:t>Console</x:t>
   </x:si>
   <x:si>
-    <x:t>Client application started. Press Enter without input to exit.
-Please enter integer number :</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-  BookId: 1,
-  Title: Harry Potter and the Philosopher's Stone,
-  PublicationYear: 1997,
-  GenreName: Fantasy
-  BookId: 3,
-  Title: The Hobbit,
-  PublicationYear: 1937,
-  GenreName: Fantasy
-Please enter integer number :</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Server started.
+    <x:t>Enter operation (format as A X B):</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Waiting for a connection from client</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Time</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Info</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Source</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Destination</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Flags</x:t>
+  </x:si>
+  <x:si>
+    <x:t>State</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SourceRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DestinationRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-11-26 12:34:35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>127.0.0.1:51971</x:t>
+  </x:si>
+  <x:si>
+    <x:t>127.0.0.1:5000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client connecting to server (SYN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server responding (SYN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection established</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DataType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Result</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ErrorCode</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ErrorCategory</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PointsAwarded</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PointsPossible</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DurationMs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DetailPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Message</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DiffIndex</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ExpectedOutput</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActualOutput</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ExpectedExcerpt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActualExcerpt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClientStdout</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Waited 1000ms</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: client output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Enter operation (format as A X B):
 </x:t>
   </x:si>
   <x:si>
-    <x:t>GET /books/1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Time</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Info</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Source</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Destination</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Flags</x:t>
-  </x:si>
-  <x:si>
-    <x:t>State</x:t>
-  </x:si>
-  <x:si>
-    <x:t>URI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Host</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Method</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Status</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HttpVersion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HttpHeaders</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HttpBody</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SourceRole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DestinationRole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2025-11-25 04:05:45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>::1:56177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>::1:8000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Client connecting to server (SYN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SYN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server responding (SYN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DataType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Result</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ErrorCode</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ErrorCategory</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PointsAwarded</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PointsPossible</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DurationMs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DetailPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Message</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DiffIndex</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ExpectedOutput</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActualOutput</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ExpectedExcerpt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActualExcerpt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ClientStdout</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Waited 1000ms</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Client application started. Press Enter without input to exit.
-Please enter integer number : 
+    <x:t xml:space="preserve">3
+Enter operation (format as A X B):
 </x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">
-  BookId: 1, 
-  Title: Harry Potter and the Philosopher's Stone, 
-  PublicationYear: 1997, 
-  GenreName: Fantasy
-  BookId: 3, 
-  Title: The Hobbit, 
-  PublicationYear: 1937, 
-  GenreName: Fantasy
-Please enter integer number : 
+    <x:t>ServerStdout</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
 </x:t>
   </x:si>
   <x:si>
-    <x:t>ServerStdout</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Server started.
-</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GET /books/1
+    <x:t xml:space="preserve">Client connected
+Client disconnected
 </x:t>
   </x:si>
   <x:si>
@@ -702,46 +665,46 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E1" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F1" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G1" s="4" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H1" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I1" s="4" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J1" s="4" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E1" s="4" t="s">
+      <x:c r="K1" s="4" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F1" s="4" t="s">
+      <x:c r="L1" s="4" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G1" s="4" t="s">
+      <x:c r="M1" s="4" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H1" s="4" t="s">
+      <x:c r="N1" s="4" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I1" s="4" t="s">
+      <x:c r="O1" s="4" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="J1" s="4" t="s">
+      <x:c r="P1" s="4" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K1" s="4" t="s">
+      <x:c r="Q1" s="4" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="L1" s="4" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="M1" s="4" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="N1" s="4" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="O1" s="4" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="P1" s="4" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="Q1" s="4" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:17" x14ac:dyDescent="0.3">
@@ -796,7 +759,7 @@
   <x:cols>
     <x:col min="20" max="16384" width="9.140625" style="1" customWidth="1"/>
     <x:col min="1" max="1" width="5.710625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="54.139196" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="30.853482" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="5.710625" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="9.424911" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="1" customWidth="1"/>
@@ -813,7 +776,7 @@
     <x:col min="16" max="16" width="13.139196" style="1" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="1" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="1" customWidth="1"/>
-    <x:col min="19" max="19" width="54.139196" style="1" customWidth="1"/>
+    <x:col min="19" max="19" width="30.853482" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -827,55 +790,55 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D1" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E1" s="4" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F1" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G1" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H1" s="4" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I1" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J1" s="4" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K1" s="4" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L1" s="4" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G1" s="4" t="s">
+      <x:c r="M1" s="4" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H1" s="4" t="s">
+      <x:c r="N1" s="4" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I1" s="4" t="s">
+      <x:c r="O1" s="4" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J1" s="4" t="s">
+      <x:c r="P1" s="4" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="K1" s="4" t="s">
+      <x:c r="Q1" s="4" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="L1" s="4" t="s">
+      <x:c r="R1" s="4" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="M1" s="4" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N1" s="4" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O1" s="4" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="P1" s="4" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="Q1" s="4" t="s">
+      <x:c r="S1" s="4" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="R1" s="4" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="S1" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:19" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    </x:row>
+    <x:row r="2" spans="1:19" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A2" s="3">
         <x:v>1</x:v>
       </x:c>
@@ -883,60 +846,58 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I2" s="1">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="J2" s="1">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="K2" s="1">
+        <x:v>6.37</x:v>
+      </x:c>
+      <x:c r="M2" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="S2" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="I2" s="1">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="J2" s="1">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="K2" s="1">
-        <x:v>4.73</x:v>
-      </x:c>
-      <x:c r="M2" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="S2" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:19" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    </x:row>
+    <x:row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <x:c r="A3" s="3">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="B3" s="3"/>
       <x:c r="F3" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I3" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J3" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K3" s="1">
+        <x:v>1010.74</x:v>
+      </x:c>
+      <x:c r="M3" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="S3" s="1" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="I3" s="1">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="J3" s="1">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="K3" s="1">
-        <x:v>0.48</x:v>
-      </x:c>
-      <x:c r="M3" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="S3" s="1" t="s">
-        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19">
@@ -944,13 +905,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>0</x:v>
@@ -959,10 +920,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K4" s="1">
-        <x:v>1016.05</x:v>
+        <x:v>1013.07</x:v>
       </x:c>
       <x:c r="M4" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -984,7 +945,7 @@
   <x:cols>
     <x:col min="20" max="16384" width="9.140625" style="1" customWidth="1"/>
     <x:col min="1" max="1" width="5.710625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="14.139196" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="33.139196" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="5.710625" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="9.424911" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="1" customWidth="1"/>
@@ -1001,7 +962,7 @@
     <x:col min="16" max="16" width="13.139196" style="1" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="1" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="1" customWidth="1"/>
-    <x:col min="19" max="19" width="14.139196" style="1" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1015,116 +976,93 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D1" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E1" s="4" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F1" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G1" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H1" s="4" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I1" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J1" s="4" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K1" s="4" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L1" s="4" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G1" s="4" t="s">
+      <x:c r="M1" s="4" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H1" s="4" t="s">
+      <x:c r="N1" s="4" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I1" s="4" t="s">
+      <x:c r="O1" s="4" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J1" s="4" t="s">
+      <x:c r="P1" s="4" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="K1" s="4" t="s">
+      <x:c r="Q1" s="4" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="L1" s="4" t="s">
+      <x:c r="R1" s="4" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="M1" s="4" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N1" s="4" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O1" s="4" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="P1" s="4" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="Q1" s="4" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="R1" s="4" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="S1" s="4" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:19" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A2" s="3">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I2" s="1">
-        <x:v>0.25</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="J2" s="1">
-        <x:v>0.25</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="K2" s="1">
-        <x:v>0.69</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="M2" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="S2" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:19" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <x:c r="A3" s="3">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H3" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="I3" s="1">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="J3" s="1">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="K3" s="1">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="M3" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
+      <x:c r="B3" s="3"/>
       <x:c r="S3" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1157,292 +1095,211 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P8"/>
+  <x:dimension ref="A1:J4"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:cols>
-    <x:col min="23" max="16384" width="9.140625" style="1" customWidth="1"/>
+    <x:col min="17" max="16384" width="9.140625" style="1" customWidth="1"/>
     <x:col min="1" max="1" width="5.710625" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="18.567768" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="5.710625" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="8.996339" style="1" customWidth="1"/>
-    <x:col min="5" max="5" width="11.139196" style="1" customWidth="1"/>
+    <x:col min="4" max="5" width="14.853482" style="1" customWidth="1"/>
     <x:col min="6" max="6" width="8.996339" style="1" customWidth="1"/>
     <x:col min="7" max="7" width="29.996339" style="1" customWidth="1"/>
-    <x:col min="8" max="9" width="5.710625" style="1" customWidth="1"/>
-    <x:col min="10" max="10" width="8.282054" style="1" customWidth="1"/>
-    <x:col min="11" max="11" width="6.424911" style="1" customWidth="1"/>
-    <x:col min="12" max="12" width="11.567768" style="1" customWidth="1"/>
-    <x:col min="13" max="13" width="12.424911" style="1" customWidth="1"/>
-    <x:col min="14" max="14" width="9.567768" style="1" customWidth="1"/>
-    <x:col min="15" max="15" width="10.853482" style="1" customWidth="1"/>
-    <x:col min="16" max="16" width="15.139196" style="1" customWidth="1"/>
-    <x:col min="17" max="17" width="10.853482" style="1" customWidth="1"/>
-    <x:col min="18" max="18" width="29.996339" style="1" customWidth="1"/>
-    <x:col min="19" max="19" width="16.424911" style="1" customWidth="1"/>
-    <x:col min="20" max="20" width="14.424911" style="1" customWidth="1"/>
-    <x:col min="21" max="21" width="10.567768" style="1" customWidth="1"/>
-    <x:col min="22" max="22" width="14.139196" style="1" customWidth="1"/>
+    <x:col min="8" max="8" width="5.710625" style="1" customWidth="1"/>
+    <x:col min="9" max="9" width="10.853482" style="1" customWidth="1"/>
+    <x:col min="10" max="10" width="15.139196" style="1" customWidth="1"/>
+    <x:col min="11" max="11" width="10.853482" style="1" customWidth="1"/>
+    <x:col min="12" max="12" width="29.996339" style="1" customWidth="1"/>
+    <x:col min="13" max="13" width="16.424911" style="1" customWidth="1"/>
+    <x:col min="14" max="14" width="14.424911" style="1" customWidth="1"/>
+    <x:col min="15" max="15" width="10.567768" style="1" customWidth="1"/>
+    <x:col min="16" max="16" width="14.139196" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:22" ht="28.8" customHeight="1" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <x:row r="1" spans="1:16" ht="28.8" customHeight="1" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <x:c r="A1" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="s">
+      <x:c r="E1" s="2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
+      <x:c r="F1" s="2" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="s">
+      <x:c r="G1" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="s">
+      <x:c r="H1" s="2" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="s">
+      <x:c r="I1" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
+      <x:c r="J1" s="2" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J1" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K1" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="L1" s="2" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="M1" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N1" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="O1" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="P1" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="Q1" s="4" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="R1" s="4" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="S1" s="4" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="T1" s="4" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="U1" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="V1" s="4" t="s">
-        <x:v>68</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:22" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="K1" s="4" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L1" s="4" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M1" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N1" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="O1" s="4" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="P1" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:16" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A2" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H2" s="3"/>
-      <x:c r="I2" s="3"/>
-      <x:c r="J2" s="3"/>
-      <x:c r="K2" s="3"/>
-      <x:c r="L2" s="3"/>
-      <x:c r="M2" s="3"/>
-      <x:c r="N2" s="3"/>
-      <x:c r="O2" s="3" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="P2" s="3" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="Q2" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="R2" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S2" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="T2" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="V2" s="5" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:22" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="I2" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J2" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L2" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="M2" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="N2" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="P2" s="5" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:16" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A3" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="s">
+      <x:c r="G3" s="3" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="s">
+      <x:c r="H3" s="3"/>
+      <x:c r="I3" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K3" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="L3" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="M3" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="N3" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="P3" s="5" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:16" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A4" s="3">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D4" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E4" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F4" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G4" s="3" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="s">
+      <x:c r="H4" s="3"/>
+      <x:c r="I4" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J4" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K4" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G3" s="3" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H3" s="3"/>
-      <x:c r="I3" s="3"/>
-      <x:c r="J3" s="3"/>
-      <x:c r="K3" s="3"/>
-      <x:c r="L3" s="3"/>
-      <x:c r="M3" s="3"/>
-      <x:c r="N3" s="3"/>
-      <x:c r="O3" s="3" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="P3" s="3" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="Q3" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="R3" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="S3" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="T3" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="V3" s="5" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <x:c r="A4" s="3"/>
-      <x:c r="B4" s="3"/>
-      <x:c r="C4" s="3"/>
-      <x:c r="D4" s="3"/>
-      <x:c r="E4" s="3"/>
-      <x:c r="F4" s="3"/>
-      <x:c r="G4" s="3"/>
-      <x:c r="H4" s="3"/>
-      <x:c r="I4" s="3"/>
-      <x:c r="J4" s="3"/>
-      <x:c r="K4" s="3"/>
-      <x:c r="L4" s="3"/>
-      <x:c r="M4" s="3"/>
-      <x:c r="N4" s="3"/>
-      <x:c r="O4" s="3"/>
-      <x:c r="P4" s="3"/>
-    </x:row>
-    <x:row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <x:c r="A5" s="3"/>
-      <x:c r="B5" s="3"/>
-      <x:c r="C5" s="3"/>
-      <x:c r="D5" s="3"/>
-      <x:c r="E5" s="3"/>
-      <x:c r="F5" s="3"/>
-      <x:c r="G5" s="3"/>
-      <x:c r="H5" s="3"/>
-      <x:c r="I5" s="3"/>
-      <x:c r="J5" s="3"/>
-      <x:c r="K5" s="3"/>
-      <x:c r="L5" s="3"/>
-      <x:c r="M5" s="3"/>
-      <x:c r="N5" s="3"/>
-      <x:c r="O5" s="3"/>
-      <x:c r="P5" s="3"/>
-    </x:row>
-    <x:row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <x:c r="A6" s="3"/>
-      <x:c r="B6" s="3"/>
-      <x:c r="C6" s="3"/>
-      <x:c r="D6" s="3"/>
-      <x:c r="E6" s="3"/>
-      <x:c r="F6" s="3"/>
-      <x:c r="G6" s="3"/>
-      <x:c r="H6" s="3"/>
-      <x:c r="I6" s="3"/>
-      <x:c r="J6" s="3"/>
-      <x:c r="K6" s="3"/>
-      <x:c r="L6" s="3"/>
-      <x:c r="M6" s="3"/>
-      <x:c r="N6" s="3"/>
-      <x:c r="O6" s="3"/>
-      <x:c r="P6" s="3"/>
-    </x:row>
-    <x:row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <x:c r="A7" s="3"/>
-      <x:c r="B7" s="3"/>
-      <x:c r="C7" s="3"/>
-      <x:c r="D7" s="3"/>
-      <x:c r="E7" s="3"/>
-      <x:c r="F7" s="3"/>
-      <x:c r="G7" s="3"/>
-      <x:c r="H7" s="3"/>
-      <x:c r="I7" s="3"/>
-      <x:c r="J7" s="3"/>
-      <x:c r="K7" s="3"/>
-      <x:c r="L7" s="3"/>
-      <x:c r="M7" s="3"/>
-      <x:c r="N7" s="3"/>
-      <x:c r="O7" s="3"/>
-      <x:c r="P7" s="3"/>
-    </x:row>
-    <x:row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <x:c r="A8" s="3"/>
-      <x:c r="B8" s="3"/>
-      <x:c r="C8" s="3"/>
-      <x:c r="D8" s="3"/>
-      <x:c r="E8" s="3"/>
-      <x:c r="F8" s="3"/>
-      <x:c r="G8" s="3"/>
-      <x:c r="H8" s="3"/>
-      <x:c r="I8" s="3"/>
-      <x:c r="J8" s="3"/>
-      <x:c r="K8" s="3"/>
-      <x:c r="L8" s="3"/>
-      <x:c r="M8" s="3"/>
-      <x:c r="N8" s="3"/>
-      <x:c r="O8" s="3"/>
-      <x:c r="P8" s="3"/>
+      <x:c r="L4" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="M4" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="N4" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="P4" s="5" t="s">
+        <x:v>45</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
